--- a/artfynd/A 6044-2024 artfynd.xlsx
+++ b/artfynd/A 6044-2024 artfynd.xlsx
@@ -999,7 +999,7 @@
         <v>130156211</v>
       </c>
       <c r="B5" t="n">
-        <v>92861</v>
+        <v>92863</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 6044-2024 artfynd.xlsx
+++ b/artfynd/A 6044-2024 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>130156209</v>
       </c>
       <c r="B3" t="n">
-        <v>79563</v>
+        <v>79648</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>130156210</v>
       </c>
       <c r="B4" t="n">
-        <v>80474</v>
+        <v>80559</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>130156211</v>
       </c>
       <c r="B5" t="n">
-        <v>92863</v>
+        <v>92950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 6044-2024 artfynd.xlsx
+++ b/artfynd/A 6044-2024 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130156209</v>
+        <v>130156210</v>
       </c>
       <c r="B3" t="n">
-        <v>79648</v>
+        <v>80559</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>374</v>
+        <v>226</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gul dropplav</t>
+          <t>Skuggorangelav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cliostomum corrugatum</t>
+          <t>Caloplaca lucifuga</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.:Fr.) Fr.</t>
+          <t>G.Thor</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>664650</v>
+        <v>664654</v>
       </c>
       <c r="R3" t="n">
-        <v>6643305</v>
+        <v>6643299</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130156210</v>
+        <v>130156209</v>
       </c>
       <c r="B4" t="n">
-        <v>80559</v>
+        <v>79648</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>226</v>
+        <v>374</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skuggorangelav</t>
+          <t>Gul dropplav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Caloplaca lucifuga</t>
+          <t>Cliostomum corrugatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>G.Thor</t>
+          <t>(Ach.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,13 +924,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>664654</v>
+        <v>664650</v>
       </c>
       <c r="R4" t="n">
-        <v>6643299</v>
+        <v>6643305</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 6044-2024 artfynd.xlsx
+++ b/artfynd/A 6044-2024 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130156210</v>
+        <v>130156209</v>
       </c>
       <c r="B3" t="n">
-        <v>80559</v>
+        <v>79648</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>226</v>
+        <v>374</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skuggorangelav</t>
+          <t>Gul dropplav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Caloplaca lucifuga</t>
+          <t>Cliostomum corrugatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>G.Thor</t>
+          <t>(Ach.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>664654</v>
+        <v>664650</v>
       </c>
       <c r="R3" t="n">
-        <v>6643299</v>
+        <v>6643305</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130156209</v>
+        <v>130156210</v>
       </c>
       <c r="B4" t="n">
-        <v>79648</v>
+        <v>80559</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>374</v>
+        <v>226</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gul dropplav</t>
+          <t>Skuggorangelav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cliostomum corrugatum</t>
+          <t>Caloplaca lucifuga</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.:Fr.) Fr.</t>
+          <t>G.Thor</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,13 +924,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>664650</v>
+        <v>664654</v>
       </c>
       <c r="R4" t="n">
-        <v>6643305</v>
+        <v>6643299</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 6044-2024 artfynd.xlsx
+++ b/artfynd/A 6044-2024 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>130156209</v>
       </c>
       <c r="B3" t="n">
-        <v>79648</v>
+        <v>79651</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>130156210</v>
       </c>
       <c r="B4" t="n">
-        <v>80559</v>
+        <v>80562</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>130156211</v>
       </c>
       <c r="B5" t="n">
-        <v>92950</v>
+        <v>92953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 6044-2024 artfynd.xlsx
+++ b/artfynd/A 6044-2024 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>130156209</v>
       </c>
       <c r="B3" t="n">
-        <v>79651</v>
+        <v>79677</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>130156210</v>
       </c>
       <c r="B4" t="n">
-        <v>80562</v>
+        <v>80588</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>130156211</v>
       </c>
       <c r="B5" t="n">
-        <v>92953</v>
+        <v>92979</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 6044-2024 artfynd.xlsx
+++ b/artfynd/A 6044-2024 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130156209</v>
+        <v>130156210</v>
       </c>
       <c r="B3" t="n">
-        <v>79677</v>
+        <v>80588</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>374</v>
+        <v>226</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gul dropplav</t>
+          <t>Skuggorangelav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cliostomum corrugatum</t>
+          <t>Caloplaca lucifuga</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.:Fr.) Fr.</t>
+          <t>G.Thor</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>664650</v>
+        <v>664654</v>
       </c>
       <c r="R3" t="n">
-        <v>6643305</v>
+        <v>6643299</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130156210</v>
+        <v>130156209</v>
       </c>
       <c r="B4" t="n">
-        <v>80588</v>
+        <v>79677</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>226</v>
+        <v>374</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skuggorangelav</t>
+          <t>Gul dropplav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Caloplaca lucifuga</t>
+          <t>Cliostomum corrugatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>G.Thor</t>
+          <t>(Ach.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,13 +924,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>664654</v>
+        <v>664650</v>
       </c>
       <c r="R4" t="n">
-        <v>6643299</v>
+        <v>6643305</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,7 +999,7 @@
         <v>130156211</v>
       </c>
       <c r="B5" t="n">
-        <v>92979</v>
+        <v>92980</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 6044-2024 artfynd.xlsx
+++ b/artfynd/A 6044-2024 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130156210</v>
+        <v>130156209</v>
       </c>
       <c r="B3" t="n">
-        <v>80588</v>
+        <v>79677</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>226</v>
+        <v>374</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skuggorangelav</t>
+          <t>Gul dropplav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Caloplaca lucifuga</t>
+          <t>Cliostomum corrugatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>G.Thor</t>
+          <t>(Ach.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>664654</v>
+        <v>664650</v>
       </c>
       <c r="R3" t="n">
-        <v>6643299</v>
+        <v>6643305</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130156209</v>
+        <v>130156210</v>
       </c>
       <c r="B4" t="n">
-        <v>79677</v>
+        <v>80588</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>374</v>
+        <v>226</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gul dropplav</t>
+          <t>Skuggorangelav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cliostomum corrugatum</t>
+          <t>Caloplaca lucifuga</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.:Fr.) Fr.</t>
+          <t>G.Thor</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,13 +924,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>664650</v>
+        <v>664654</v>
       </c>
       <c r="R4" t="n">
-        <v>6643305</v>
+        <v>6643299</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,7 +999,7 @@
         <v>130156211</v>
       </c>
       <c r="B5" t="n">
-        <v>92980</v>
+        <v>92981</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
